--- a/poker/resources/sample/poolresults.xlsx
+++ b/poker/resources/sample/poolresults.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="poolresults" sheetId="1" r:id="rId1"/>
@@ -36,24 +36,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
             <sz val="16"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-下注下限&amp;下注上限，模式ID，第X个倍数档位-修改后权重值|……；模式ID，第X个倍数档位-修改后权重值|……#下注下限&amp;下注上限，模式ID，第X个倍数档位-修改后权重值|……；模式ID，第X个倍数档位-修改后权重值|……
-1&amp;500000_1,3-0|4-0|5-0#500000&amp;999999999_1,0-0|1-0|2-0;2,4-0|5-0;3,6-0#
-下注金额在1~500000内时，常规模式（1）中5-10倍、10-15倍、15-20倍中奖权重改为0
-下注金额在500000~999999999时，常规模式（1）中0-1倍、1-2倍、2-5倍中奖权重改为0；樱桃模式（2）中10-15倍、15-20倍中奖权重改为0；明星模式中（3）中20-50倍中奖权重改为0
+          <t xml:space="preserve">[{[倍数区间下限,倍数区间上限],权重值},{[倍数区间下限,倍数区间上限],权重值}]}]
 </t>
         </r>
       </text>
@@ -104,362 +91,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>倍数区间</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>ID_权重
-倍数区间ID：
-1：72-78
-2：65-72
-3：58-65
-4：52-58
-5：45-52
-6：39-45
-7：32-39
-8：26-32
-9：19-26
-10：13-19
-11:6-13
-12:0-6
-13:-6-0
-14:-13_-6
-15:-19_-13
-16:-26_-19
-17:-32_-26
-18:-32以上</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>倍数区间</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>ID_权重
-倍数区间ID：
-1：72-78
-2：65-72
-3：58-65
-4：52-58
-5：45-52
-6：39-45
-7：32-39
-8：26-32
-9：19-26
-10：13-19
-11:6-13
-12:0-6
-13:-6-0
-14:-13_-6
-15:-19_-13
-16:-26_-19
-17:-32_-26
-18:-32以上</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>倍数区间</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>ID_权重
-倍数区间ID：
-1：72-78
-2：65-72
-3：58-65
-4：52-58
-5：45-52
-6：39-45
-7：32-39
-8：26-32
-9：19-26
-10：13-19
-11:6-13
-12:0-6
-13:-6-0
-14:-13_-6
-15:-19_-13
-16:-26_-19
-17:-32_-26
-18:-32以上</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>倍数区间</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>ID_权重
-倍数区间ID：
-1：72-78
-2：65-72
-3：58-65
-4：52-58
-5：45-52
-6：39-45
-7：32-39
-8：26-32
-9：19-26
-10：13-19
-11:6-13
-12:0-6
-13:-6-0
-14:-13_-6
-15:-19_-13
-16:-26_-19
-17:-32_-26
-18:-32以上</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>倍数区间</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>ID_权重
-倍数区间ID：
-1：72-78
-2：65-72
-3：58-65
-4：52-58
-5：45-52
-6：39-45
-7：32-39
-8：26-32
-9：19-26
-10：13-19
-11:6-13
-12:0-6
-13:-6-0
-14:-13_-6
-15:-19_-13
-16:-26_-19
-17:-32_-26
-18:-32以上</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>倍数区间</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>ID_权重
-倍数区间ID：
-1：72-78
-2：65-72
-3：58-65
-4：52-58
-5：45-52
-6：39-45
-7：32-39
-8：26-32
-9：19-26
-10：13-19
-11:6-13
-12:0-6
-13:-6-0
-14:-13_-6
-15:-19_-13
-16:-26_-19
-17:-32_-26
-18:-32以上</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">Administrator:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>倍数区间</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="16"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>ID_权重
-倍数区间ID：
-1：72-78
-2：65-72
-3：58-65
-4：52-58
-5：45-52
-6：39-45
-7：32-39
-8：26-32
-9：19-26
-10：13-19
-11:6-13
-12:0-6
-13:-6-0
-14:-13_-6
-15:-19_-13
-16:-26_-19
-17:-32_-26
-18:-32以上</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -473,7 +110,7 @@
     <t>连输修改权重</t>
   </si>
   <si>
-    <t>类型权重</t>
+    <t>倍数区间及权重</t>
   </si>
   <si>
     <t>进入条件下线</t>
@@ -515,49 +152,76 @@
     <t>南方前进</t>
   </si>
   <si>
-    <t>-6:-99999_0|-39_-200|-32_-200|-26_-200|-19_-200|-6_-200|0_200|3_200|6_200|13_200|19_200|32_200|52_200|72_200|99999_200;-3:-99999_0|-39_-100|-32_-100|-26_-100|-19_-100|-6_-100|0_100|3_100|6_100|13_100|19_100|32_100|52_100|72_100|99999_100;0:-99999_0|-39_0|-32_0|-26_0|-19_0|-6_0|0_0|3_0|6_0|13_0|19_0|32_0|52_0|72_0|99999_0;3:-99999_0|-39_100|-32_100|-26_100|-19_100|-6_100|0_-100|3_-100|6_-100|13_-100|19_-100|32_-100|52_-100|72_-100|99999_-100;6:-99999_0|-39_100|-32_100|-26_100|-19_100|-6_100|0_-100|3_-100|6_-100|13_-100|19_-100|32_-100|52_-100|72_-100|99999_-100;</t>
-  </si>
-  <si>
-    <t>-99999:300|-39:200|-32:300|-26:200|-19:300|-13:300|-6:300|0:300|6:300|13:300|19:300|32:300|52:300|72:300|78:300|99999:300</t>
+    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:150|-26:140|-19:130|-13:110|-6:100|0:90|6:110|13:140|19:130|26:120|32:120|39:120|45:110|52:100|58:90|65:80|72:70|78:60|99999:0</t>
   </si>
   <si>
     <t>放水池+3</t>
   </si>
   <si>
-    <t>-99999:300|-39:200|-32:300|-26:200|-19:300|-13:300|-6:300|0:300|6:300|13:300|19:300|32:300|52:300|72:300|78:300|99999:301</t>
+    <t>103%-105%</t>
+  </si>
+  <si>
+    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-101;</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:180|-26:160|-19:140|-13:120|-6:100|0:90|6:120|13:150|19:130|26:110|32:100|39:100|45:90|52:80|58:60|65:40|72:30|78:20|99999:0</t>
   </si>
   <si>
     <t>放水池+2</t>
   </si>
   <si>
-    <t>-99999:300|-39:200|-32:300|-26:200|-19:300|-13:300|-6:300|0:300|6:300|13:300|19:300|32:300|52:300|72:300|78:300|99999:302</t>
+    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-102;</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:200|-26:180|-19:150|-13:130|-6:110|0:100|6:130|13:160|19:140|26:120|32:110|39:90|45:70|52:50|58:30|65:20|72:10|78:10|99999:0</t>
   </si>
   <si>
     <t>放水池+1</t>
   </si>
   <si>
-    <t>-99999:300|-39:200|-32:300|-26:200|-19:300|-13:300|-6:300|0:300|6:300|13:300|19:300|32:300|52:300|72:300|78:300|99999:303</t>
+    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-103;</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:220|-26:200|-19:160|-13:140|-6:100|0:90|6:120|13:150|19:130|26:110|32:90|39:70|45:50|52:30|58:20|65:10|72:5|78:5|99999:0</t>
   </si>
   <si>
     <t>标准池</t>
   </si>
   <si>
-    <t>-99999:300|-39:200|-32:300|-26:200|-19:300|-13:300|-6:300|0:300|6:300|13:300|19:300|32:300|52:300|72:300|78:300|99999:304</t>
+    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-104;</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:250|-26:220|-19:150|-13:120|-6:80|0:70|6:60|13:40|19:30|26:20|32:15|39:12|45:10|52:8|58:6|65:4|72:2|78:2|99999:0</t>
   </si>
   <si>
     <t>吸水池-1</t>
   </si>
   <si>
-    <t>-99999:300|-39:200|-32:300|-26:200|-19:300|-13:300|-6:300|0:300|6:300|13:300|19:300|32:300|52:300|72:300|78:300|99999:305</t>
+    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-105;</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:280|-26:230|-19:140|-13:100|-6:60|0:50|6:40|13:30|19:20|26:15|32:10|39:8|45:6|52:4|58:3|65:2|72:1|78:1|99999:0</t>
   </si>
   <si>
     <t>吸水池-2</t>
   </si>
   <si>
-    <t>-99999:300|-39:200|-32:300|-26:200|-19:300|-13:300|-6:300|0:300|6:300|13:300|19:300|32:300|52:300|72:300|78:300|99999:306</t>
+    <t>94%-95%</t>
+  </si>
+  <si>
+    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-106;</t>
+  </si>
+  <si>
+    <t>-99999:0|-32:300|-26:250|-19:150|-13:100|-6:50|0:40|6:30|13:20|19:15|26:10|32:5|39:4|45:3|52:2|58:1|65:1|72:1|78:1|99999:0</t>
   </si>
   <si>
     <t>吸水池-3</t>
+  </si>
+  <si>
+    <t>92%-94%</t>
   </si>
 </sst>
 </file>
@@ -570,7 +234,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,23 +393,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1200,7 +852,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1232,11 +884,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1558,7 +1219,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
@@ -1569,9 +1230,10 @@
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
+    <col min="10" max="10" width="16.7833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:9">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:9">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1623,7 +1285,7 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" ht="16.5" spans="1:9">
+    <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1648,7 +1310,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" ht="16.5" spans="1:9">
+    <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1659,7 +1321,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" ht="16.5" spans="1:9">
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="6">
         <v>4001</v>
       </c>
@@ -1672,10 +1334,10 @@
       <c r="D5" s="8">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="9" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="10">
@@ -1687,8 +1349,11 @@
       <c r="I5" s="10" t="s">
         <v>20</v>
       </c>
+      <c r="J5" s="11" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" ht="16.5" spans="1:9">
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="6">
         <v>4002</v>
       </c>
@@ -1701,11 +1366,11 @@
       <c r="D6" s="8">
         <v>2</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>21</v>
+      <c r="E6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="G6" s="10">
         <v>6000</v>
@@ -1714,10 +1379,13 @@
         <v>8000</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="J6" s="12">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" ht="16.5" spans="1:9">
+    <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="6">
         <v>4003</v>
       </c>
@@ -1730,11 +1398,11 @@
       <c r="D7" s="8">
         <v>3</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>23</v>
+      <c r="E7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="G7" s="10">
         <v>4000</v>
@@ -1743,10 +1411,13 @@
         <v>6000</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0.985</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:9">
+    <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="6">
         <v>4004</v>
       </c>
@@ -1759,11 +1430,11 @@
       <c r="D8" s="8">
         <v>4</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>25</v>
+      <c r="E8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="G8" s="10">
         <v>2000</v>
@@ -1772,10 +1443,13 @@
         <v>4000</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0.97</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:9">
+    <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="6">
         <v>4005</v>
       </c>
@@ -1788,11 +1462,11 @@
       <c r="D9" s="8">
         <v>5</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>27</v>
+      <c r="E9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -1801,10 +1475,13 @@
         <v>2000</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>28</v>
+        <v>33</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0.96</v>
       </c>
     </row>
-    <row r="10" ht="16.5" spans="1:9">
+    <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="6">
         <v>4006</v>
       </c>
@@ -1817,11 +1494,11 @@
       <c r="D10" s="8">
         <v>6</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>29</v>
+      <c r="E10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="G10" s="10">
         <v>-1000</v>
@@ -1830,10 +1507,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>30</v>
+        <v>36</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="11" ht="16.5" spans="1:9">
+    <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="6">
         <v>4007</v>
       </c>
@@ -1846,11 +1526,11 @@
       <c r="D11" s="8">
         <v>7</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>31</v>
+      <c r="E11" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="G11" s="10">
         <v>-999999</v>
@@ -1859,10 +1539,13 @@
         <v>-1000</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>32</v>
+        <v>40</v>
+      </c>
+      <c r="J11" s="14" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="6"/>
     </row>
   </sheetData>

--- a/poker/resources/sample/poolresults.xlsx
+++ b/poker/resources/sample/poolresults.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="14160" windowHeight="7485"/>
   </bookViews>
   <sheets>
-    <sheet name="poolresults" sheetId="1" r:id="rId1"/>
+    <sheet name="poolResults" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -152,7 +153,7 @@
     <t>南方前进</t>
   </si>
   <si>
-    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;</t>
+    <t>-5:-99999_0|-32_500|-26_500|-19_500|-13_500|-6_500|0_500|6_500|13_500|19_500|26_500|32_500|39_500|45_500|52_500|58_500|65_500|72_500|78_500|99999_0;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;5:-99999_0|-32_350|-26_-350|-19_-350|-13_-350|-6_-350|0_-350|6_-350|13_-350|19_-350|26_-350|32_-350|39_-350|45_-350|52_-350|58_-350|65_-350|72_-350|78_-350|99999_0</t>
   </si>
   <si>
     <t>-99999:0|-32:150|-26:140|-19:130|-13:110|-6:100|0:90|6:110|13:140|19:130|26:120|32:120|39:120|45:110|52:100|58:90|65:80|72:70|78:60|99999:0</t>
@@ -164,45 +165,30 @@
     <t>103%-105%</t>
   </si>
   <si>
-    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-101;</t>
-  </si>
-  <si>
     <t>-99999:0|-32:180|-26:160|-19:140|-13:120|-6:100|0:90|6:120|13:150|19:130|26:110|32:100|39:100|45:90|52:80|58:60|65:40|72:30|78:20|99999:0</t>
   </si>
   <si>
     <t>放水池+2</t>
   </si>
   <si>
-    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-102;</t>
-  </si>
-  <si>
     <t>-99999:0|-32:200|-26:180|-19:150|-13:130|-6:110|0:100|6:130|13:160|19:140|26:120|32:110|39:90|45:70|52:50|58:30|65:20|72:10|78:10|99999:0</t>
   </si>
   <si>
     <t>放水池+1</t>
   </si>
   <si>
-    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-103;</t>
-  </si>
-  <si>
     <t>-99999:0|-32:220|-26:200|-19:160|-13:140|-6:100|0:90|6:120|13:150|19:130|26:110|32:90|39:70|45:50|52:30|58:20|65:10|72:5|78:5|99999:0</t>
   </si>
   <si>
     <t>标准池</t>
   </si>
   <si>
-    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-104;</t>
-  </si>
-  <si>
     <t>-99999:0|-32:250|-26:220|-19:150|-13:120|-6:80|0:70|6:60|13:40|19:30|26:20|32:15|39:12|45:10|52:8|58:6|65:4|72:2|78:2|99999:0</t>
   </si>
   <si>
     <t>吸水池-1</t>
   </si>
   <si>
-    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-105;</t>
-  </si>
-  <si>
     <t>-99999:0|-32:280|-26:230|-19:140|-13:100|-6:60|0:50|6:40|13:30|19:20|26:15|32:10|39:8|45:6|52:4|58:3|65:2|72:1|78:1|99999:0</t>
   </si>
   <si>
@@ -212,9 +198,6 @@
     <t>94%-95%</t>
   </si>
   <si>
-    <t>-6:-99999_0|-32_-200|-26_-200|-19_-200|-13_-200|-6_-200|0_200|6_200|13_200|19_200|26_200|32_200|39_200|45_200|52_200|58_200|65_200|72_200|78_200|99999_200;-3:-99999_0|-32_-100|-26_-100|-19_-100|-13_-100|-6_-100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_100;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;3:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-100;6:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_-100|6_-100|13_-100|19_-100|26_-100|32_-100|39_-100|45_-100|52_-100|58_-100|65_-100|72_-100|78_-100|99999_-106;</t>
-  </si>
-  <si>
     <t>-99999:0|-32:300|-26:250|-19:150|-13:100|-6:50|0:40|6:30|13:20|19:15|26:10|32:5|39:4|45:3|52:2|58:1|65:1|72:1|78:1|99999:0</t>
   </si>
   <si>
@@ -222,6 +205,18 @@
   </si>
   <si>
     <t>92%-94%</t>
+  </si>
+  <si>
+    <t>体验优化法（平滑）</t>
+  </si>
+  <si>
+    <t>-5:-99999_0|-32_10|-26_20|-19_30|-13_40|-6_50|0_60|6_70|13_80|19_90|26_100|32_110|39_120|45_130|52_140|58_150|65_160|72_170|78_180|99999_0;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;5:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_1000|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0</t>
+  </si>
+  <si>
+    <t>暴力覆盖法</t>
+  </si>
+  <si>
+    <t>-5:-99999_0|-32_100|-26_100|-19_100|-13_100|-6_100|0_100|6_100|13_100|19_100|26_100|32_100|39_100|45_100|52_100|58_100|65_100|72_100|78_100|99999_0;0:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_0|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0;5:-99999_0|-32_0|-26_0|-19_0|-13_0|-6_0|0_1000|6_0|13_0|19_0|26_0|32_0|39_0|45_0|52_0|58_0|65_0|72_0|78_0|99999_0</t>
   </si>
 </sst>
 </file>
@@ -234,7 +229,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +240,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -721,139 +722,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -892,12 +895,6 @@
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1219,14 +1216,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.25"/>
     <col min="2" max="3" width="15.25" customWidth="1"/>
     <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="99.2916666666667" customWidth="1"/>
-    <col min="6" max="6" width="120.35" style="1" customWidth="1"/>
+    <col min="6" max="6" width="120.35" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.625" customWidth="1"/>
     <col min="8" max="8" width="15.125" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
@@ -1234,323 +1231,379 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="2"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="2"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="6">
+      <c r="A5" s="8">
         <v>4001</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="8">
         <v>300400</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="10">
         <v>1</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="12">
         <v>8000</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="12">
         <v>999999</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="13" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="6">
+      <c r="A6" s="8">
         <v>4002</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="8">
         <v>300400</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="10">
         <v>2</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="12">
+        <v>6000</v>
+      </c>
+      <c r="H6" s="12">
+        <v>8000</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="10">
+      <c r="J6" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:10">
+      <c r="A7" s="8">
+        <v>4003</v>
+      </c>
+      <c r="B7" s="8">
+        <v>300400</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="10">
+        <v>3</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="12">
+        <v>4000</v>
+      </c>
+      <c r="H7" s="12">
         <v>6000</v>
       </c>
-      <c r="H6" s="10">
-        <v>8000</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="6">
-        <v>4003</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="I7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0.985</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:10">
+      <c r="A8" s="8">
+        <v>4004</v>
+      </c>
+      <c r="B8" s="8">
         <v>300400</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="8">
-        <v>3</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="D8" s="10">
+        <v>4</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G8" s="12">
+        <v>2000</v>
+      </c>
+      <c r="H8" s="12">
         <v>4000</v>
       </c>
-      <c r="H7" s="10">
-        <v>6000</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="I8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="13">
-        <v>0.985</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:10">
-      <c r="A8" s="6">
-        <v>4004</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="J8" s="14">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:10">
+      <c r="A9" s="8">
+        <v>4005</v>
+      </c>
+      <c r="B9" s="8">
         <v>300400</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="8">
-        <v>4</v>
-      </c>
-      <c r="E8" s="15" t="s">
+      <c r="D9" s="10">
+        <v>5</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="10">
-        <v>2000</v>
-      </c>
-      <c r="H8" s="10">
-        <v>4000</v>
-      </c>
-      <c r="I8" s="10" t="s">
+      <c r="J9" s="14">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:10">
+      <c r="A10" s="8">
+        <v>4006</v>
+      </c>
+      <c r="B10" s="8">
+        <v>300400</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="10">
+        <v>6</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="12">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="6">
-        <v>4005</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="G10" s="12">
+        <v>-1000</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:10">
+      <c r="A11" s="8">
+        <v>4007</v>
+      </c>
+      <c r="B11" s="8">
         <v>300400</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C11" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="8">
-        <v>5</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="10">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <v>2000</v>
-      </c>
-      <c r="I9" s="10" t="s">
+      <c r="D11" s="10">
+        <v>7</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="12">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="6">
-        <v>4006</v>
-      </c>
-      <c r="B10" s="6">
-        <v>300400</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="8">
-        <v>6</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="G11" s="12">
+        <v>-999999</v>
+      </c>
+      <c r="H11" s="12">
+        <v>-1000</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="J11" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="10">
-        <v>-1000</v>
-      </c>
-      <c r="H10" s="10">
-        <v>0</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:10">
-      <c r="A11" s="6">
-        <v>4007</v>
-      </c>
-      <c r="B11" s="6">
-        <v>300400</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="8">
-        <v>7</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="G11" s="10">
-        <v>-999999</v>
-      </c>
-      <c r="H11" s="10">
-        <v>-1000</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="6"/>
+      <c r="A12" s="8"/>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="17.25" spans="5:6">
+      <c r="E37" s="2"/>
+      <c r="F37" s="13"/>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="17.25" spans="5:6">
+      <c r="E38" s="2"/>
+      <c r="F38" s="13"/>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="17.25" spans="5:6">
+      <c r="E39" s="2"/>
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="16.5" spans="5:6">
+      <c r="F40" s="13"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="16.5" spans="5:6">
+      <c r="F41" s="13"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="16.5" spans="5:6">
+      <c r="F42" s="13"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="16.5" spans="5:6">
+      <c r="F43" s="13"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="16.5" spans="5:6">
+      <c r="F44" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A13:C15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="13" ht="27" customHeight="1"/>
+    <row r="14" ht="17.25" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>